--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06925177574157715</v>
+        <v>0.06598377227783203</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999999999969686</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09426283836364746</v>
+        <v>0.09597182273864746</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999999999968388</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06925177574157715</v>
+        <v>0.06598377227783203</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999999999969686</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09426283836364746</v>
+        <v>0.09597182273864746</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999999999968388</v>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06598377227783203</v>
+        <v>0.1402401924133301</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999999999969686</v>
+        <v>0.9095325244128653</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999999999964098</v>
+        <v>0.9134070331993437</v>
       </c>
       <c r="G2" t="n">
-        <v>3.733994582140021e-05</v>
+        <v>5.798964155976802</v>
       </c>
       <c r="H2" t="n">
-        <v>2.734276452877381e-05</v>
+        <v>4.192993498939789</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 0.5, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 1e-05, 'l1_ratio': 1.0, 'selection': 'random'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09597182273864746</v>
+        <v>0.1987051963806152</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999999999968388</v>
+        <v>0.9087558070992785</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999999999964098</v>
+        <v>0.9133757607379048</v>
       </c>
       <c r="G3" t="n">
-        <v>3.733994582140021e-05</v>
+        <v>5.800011189699457</v>
       </c>
       <c r="H3" t="n">
-        <v>2.734276452877381e-05</v>
+        <v>4.193244794799755</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 0.5, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 1e-05, 'l1_ratio': 0.7, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06598377227783203</v>
+        <v>0.1402401924133301</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999999999969686</v>
+        <v>0.9095325244128653</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999999999964098</v>
+        <v>0.9134070331993437</v>
       </c>
       <c r="G2" t="n">
-        <v>3.733994582140021e-05</v>
+        <v>5.798964155976802</v>
       </c>
       <c r="H2" t="n">
-        <v>2.734276452877381e-05</v>
+        <v>4.192993498939789</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 0.5, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 1e-05, 'l1_ratio': 1.0, 'selection': 'random'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09597182273864746</v>
+        <v>0.1987051963806152</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999999999968388</v>
+        <v>0.9087558070992785</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999999999964098</v>
+        <v>0.9133757607379048</v>
       </c>
       <c r="G3" t="n">
-        <v>3.733994582140021e-05</v>
+        <v>5.800011189699457</v>
       </c>
       <c r="H3" t="n">
-        <v>2.734276452877381e-05</v>
+        <v>4.193244794799755</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 0.5, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 1e-05, 'l1_ratio': 0.7, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1402401924133301</v>
+        <v>12.5073721408844</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095325244128653</v>
+        <v>0.3876262051339365</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.3881622402889363</v>
       </c>
       <c r="G2" t="n">
-        <v>5.798964155976802</v>
+        <v>139.1908557787723</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192993498939789</v>
+        <v>104.7956211318626</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 1.0, 'selection': 'random'}</t>
+          <t>{'alpha': 1e-05, 'l1_ratio': 0.1, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1987051963806152</v>
+        <v>12.90016484260559</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087558070992785</v>
+        <v>0.3875178131273947</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133757607379048</v>
+        <v>0.3881622402889363</v>
       </c>
       <c r="G3" t="n">
-        <v>5.800011189699457</v>
+        <v>139.1908557787723</v>
       </c>
       <c r="H3" t="n">
-        <v>4.193244794799755</v>
+        <v>104.7956211318626</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 0.7, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 1e-05, 'l1_ratio': 0.1, 'selection': 'cyclic'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>15.39499068260193</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3874170267044232</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3881622402889363</v>
+      </c>
+      <c r="G4" t="n">
+        <v>139.1908557787723</v>
+      </c>
+      <c r="H4" t="n">
+        <v>104.7956211318626</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'l1_ratio': 0.1, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1402401924133301</v>
+        <v>12.5073721408844</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095325244128653</v>
+        <v>0.3876262051339365</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.3881622402889363</v>
       </c>
       <c r="G2" t="n">
-        <v>5.798964155976802</v>
+        <v>139.1908557787723</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192993498939789</v>
+        <v>104.7956211318626</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 1.0, 'selection': 'random'}</t>
+          <t>{'alpha': 1e-05, 'l1_ratio': 0.1, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1987051963806152</v>
+        <v>12.90016484260559</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087558070992785</v>
+        <v>0.3875178131273947</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133757607379048</v>
+        <v>0.3881622402889363</v>
       </c>
       <c r="G3" t="n">
-        <v>5.800011189699457</v>
+        <v>139.1908557787723</v>
       </c>
       <c r="H3" t="n">
-        <v>4.193244794799755</v>
+        <v>104.7956211318626</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 0.7, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 1e-05, 'l1_ratio': 0.1, 'selection': 'cyclic'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>15.39499068260193</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3874170267044232</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3881622402889363</v>
+      </c>
+      <c r="G4" t="n">
+        <v>139.1908557787723</v>
+      </c>
+      <c r="H4" t="n">
+        <v>104.7956211318626</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'l1_ratio': 0.1, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>12.5073721408844</v>
+        <v>0.09876132011413574</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3876262051339365</v>
+        <v>0.9095174369097344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3881622402889363</v>
+        <v>0.9133112678275858</v>
       </c>
       <c r="G2" t="n">
-        <v>139.1908557787723</v>
+        <v>5.802169881120578</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7956211318626</v>
+        <v>4.19427635989441</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 0.1, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 0.001, 'l1_ratio': 1.0, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>12.90016484260559</v>
+        <v>0.1238057613372803</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3875178131273947</v>
+        <v>0.9087447139966063</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3881622402889363</v>
+        <v>0.9133112678275858</v>
       </c>
       <c r="G3" t="n">
-        <v>139.1908557787723</v>
+        <v>5.802169881120578</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7956211318626</v>
+        <v>4.19427635989441</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 0.1, 'selection': 'cyclic'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ElasticNet</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>15.39499068260193</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.3874170267044232</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.3881622402889363</v>
-      </c>
-      <c r="G4" t="n">
-        <v>139.1908557787723</v>
-      </c>
-      <c r="H4" t="n">
-        <v>104.7956211318626</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 0.1, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 0.001, 'l1_ratio': 1.0, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>12.5073721408844</v>
+        <v>0.09876132011413574</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3876262051339365</v>
+        <v>0.9095174369097344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3881622402889363</v>
+        <v>0.9133112678275858</v>
       </c>
       <c r="G2" t="n">
-        <v>139.1908557787723</v>
+        <v>5.802169881120578</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7956211318626</v>
+        <v>4.19427635989441</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 0.1, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 0.001, 'l1_ratio': 1.0, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>12.90016484260559</v>
+        <v>0.1238057613372803</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3875178131273947</v>
+        <v>0.9087447139966063</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3881622402889363</v>
+        <v>0.9133112678275858</v>
       </c>
       <c r="G3" t="n">
-        <v>139.1908557787723</v>
+        <v>5.802169881120578</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7956211318626</v>
+        <v>4.19427635989441</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 0.1, 'selection': 'cyclic'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ElasticNet</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>15.39499068260193</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.3874170267044232</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.3881622402889363</v>
-      </c>
-      <c r="G4" t="n">
-        <v>139.1908557787723</v>
-      </c>
-      <c r="H4" t="n">
-        <v>104.7956211318626</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 0.1, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 0.001, 'l1_ratio': 1.0, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09876132011413574</v>
+        <v>0.2229351997375488</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095174369097344</v>
+        <v>0.9095307134779663</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133112678275858</v>
+        <v>0.9133998765984722</v>
       </c>
       <c r="G2" t="n">
-        <v>5.802169881120578</v>
+        <v>5.799203782912025</v>
       </c>
       <c r="H2" t="n">
-        <v>4.19427635989441</v>
+        <v>4.192790055171488</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'l1_ratio': 1.0, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 0.0001, 'l1_ratio': 1.0, 'max_iter': 10000, 'selection': 'random'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1238057613372803</v>
+        <v>0.2479968070983887</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087447139966063</v>
+        <v>0.9087514890888293</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133112678275858</v>
+        <v>0.9133998765984722</v>
       </c>
       <c r="G3" t="n">
-        <v>5.802169881120578</v>
+        <v>5.799203782912025</v>
       </c>
       <c r="H3" t="n">
-        <v>4.19427635989441</v>
+        <v>4.192790055171488</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'l1_ratio': 1.0, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 0.0001, 'l1_ratio': 1.0, 'max_iter': 10000, 'selection': 'random'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09876132011413574</v>
+        <v>0.2229351997375488</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095174369097344</v>
+        <v>0.9095307134779663</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133112678275858</v>
+        <v>0.9133998765984722</v>
       </c>
       <c r="G2" t="n">
-        <v>5.802169881120578</v>
+        <v>5.799203782912025</v>
       </c>
       <c r="H2" t="n">
-        <v>4.19427635989441</v>
+        <v>4.192790055171488</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'l1_ratio': 1.0, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 0.0001, 'l1_ratio': 1.0, 'max_iter': 10000, 'selection': 'random'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1238057613372803</v>
+        <v>0.2479968070983887</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087447139966063</v>
+        <v>0.9087514890888293</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133112678275858</v>
+        <v>0.9133998765984722</v>
       </c>
       <c r="G3" t="n">
-        <v>5.802169881120578</v>
+        <v>5.799203782912025</v>
       </c>
       <c r="H3" t="n">
-        <v>4.19427635989441</v>
+        <v>4.192790055171488</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'l1_ratio': 1.0, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 0.0001, 'l1_ratio': 1.0, 'max_iter': 10000, 'selection': 'random'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2229351997375488</v>
+        <v>0.0794675350189209</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095307134779663</v>
+        <v>0.909533215133945</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133998765984722</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G2" t="n">
-        <v>5.799203782912025</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192790055171488</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.0001, 'l1_ratio': 1.0, 'max_iter': 10000, 'selection': 'random'}</t>
+          <t>{'alpha': 0.001, 'l1_ratio': 0.7, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2479968070983887</v>
+        <v>0.09433722496032715</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087514890888293</v>
+        <v>0.9087632939524625</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133998765984722</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G3" t="n">
-        <v>5.799203782912025</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192790055171488</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.0001, 'l1_ratio': 1.0, 'max_iter': 10000, 'selection': 'random'}</t>
+          <t>{'alpha': 0.001, 'l1_ratio': 0.7, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2229351997375488</v>
+        <v>0.0794675350189209</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095307134779663</v>
+        <v>0.909533215133945</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133998765984722</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G2" t="n">
-        <v>5.799203782912025</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192790055171488</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.0001, 'l1_ratio': 1.0, 'max_iter': 10000, 'selection': 'random'}</t>
+          <t>{'alpha': 0.001, 'l1_ratio': 0.7, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2479968070983887</v>
+        <v>0.09433722496032715</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087514890888293</v>
+        <v>0.9087632939524625</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133998765984722</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G3" t="n">
-        <v>5.799203782912025</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192790055171488</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.0001, 'l1_ratio': 1.0, 'max_iter': 10000, 'selection': 'random'}</t>
+          <t>{'alpha': 0.001, 'l1_ratio': 0.7, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0794675350189209</v>
+        <v>0.0752718448638916</v>
       </c>
       <c r="E2" t="n">
         <v>0.909533215133945</v>
@@ -507,7 +507,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'l1_ratio': 0.7, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09433722496032715</v>
+        <v>0.08637738227844238</v>
       </c>
       <c r="E3" t="n">
         <v>0.9087632939524625</v>
@@ -542,7 +542,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'l1_ratio': 0.7, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0794675350189209</v>
+        <v>0.0752718448638916</v>
       </c>
       <c r="E2" t="n">
         <v>0.909533215133945</v>
@@ -638,7 +638,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'l1_ratio': 0.7, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09433722496032715</v>
+        <v>0.08637738227844238</v>
       </c>
       <c r="E3" t="n">
         <v>0.9087632939524625</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'l1_ratio': 0.7, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0752718448638916</v>
+        <v>11.87900996208191</v>
       </c>
       <c r="E2" t="n">
-        <v>0.909533215133945</v>
+        <v>0.387611695296131</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133122243111836</v>
+        <v>0.3880771257287021</v>
       </c>
       <c r="G2" t="n">
-        <v>5.802137871795419</v>
+        <v>139.2005370678847</v>
       </c>
       <c r="H2" t="n">
-        <v>4.193872563312008</v>
+        <v>104.7953480310862</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08637738227844238</v>
+        <v>35.07627987861633</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087632939524625</v>
+        <v>0.3875075500335963</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133122243111836</v>
+        <v>0.3880771257287021</v>
       </c>
       <c r="G3" t="n">
-        <v>5.802137871795419</v>
+        <v>139.2005370678847</v>
       </c>
       <c r="H3" t="n">
-        <v>4.193872563312008</v>
+        <v>104.7953480310862</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0752718448638916</v>
+        <v>11.87900996208191</v>
       </c>
       <c r="E2" t="n">
-        <v>0.909533215133945</v>
+        <v>0.387611695296131</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133122243111836</v>
+        <v>0.3880771257287021</v>
       </c>
       <c r="G2" t="n">
-        <v>5.802137871795419</v>
+        <v>139.2005370678847</v>
       </c>
       <c r="H2" t="n">
-        <v>4.193872563312008</v>
+        <v>104.7953480310862</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08637738227844238</v>
+        <v>35.07627987861633</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087632939524625</v>
+        <v>0.3875075500335963</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133122243111836</v>
+        <v>0.3880771257287021</v>
       </c>
       <c r="G3" t="n">
-        <v>5.802137871795419</v>
+        <v>139.2005370678847</v>
       </c>
       <c r="H3" t="n">
-        <v>4.193872563312008</v>
+        <v>104.7953480310862</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>11.87900996208191</v>
+        <v>0.07013201713562012</v>
       </c>
       <c r="E2" t="n">
-        <v>0.387611695296131</v>
+        <v>0.2766903121172088</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3880771257287021</v>
+        <v>0.2616875221828251</v>
       </c>
       <c r="G2" t="n">
-        <v>139.2005370678847</v>
+        <v>0.7561766858252632</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7953480310862</v>
+        <v>0.5882492388088877</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>35.07627987861633</v>
+        <v>0.08591938018798828</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3875075500335963</v>
+        <v>0.2779434303402907</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3880771257287021</v>
+        <v>0.2616875221828251</v>
       </c>
       <c r="G3" t="n">
-        <v>139.2005370678847</v>
+        <v>0.7561766858252632</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7953480310862</v>
+        <v>0.5882492388088877</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>11.87900996208191</v>
+        <v>0.07013201713562012</v>
       </c>
       <c r="E2" t="n">
-        <v>0.387611695296131</v>
+        <v>0.2766903121172088</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3880771257287021</v>
+        <v>0.2616875221828251</v>
       </c>
       <c r="G2" t="n">
-        <v>139.2005370678847</v>
+        <v>0.7561766858252632</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7953480310862</v>
+        <v>0.5882492388088877</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>35.07627987861633</v>
+        <v>0.08591938018798828</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3875075500335963</v>
+        <v>0.2779434303402907</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3880771257287021</v>
+        <v>0.2616875221828251</v>
       </c>
       <c r="G3" t="n">
-        <v>139.2005370678847</v>
+        <v>0.7561766858252632</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7953480310862</v>
+        <v>0.5882492388088877</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07013201713562012</v>
+        <v>8.003521919250488</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2766903121172088</v>
+        <v>0.1631195370408529</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2616875221828251</v>
+        <v>0.1688718910031372</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7561766858252632</v>
+        <v>91.1985454794509</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5882492388088877</v>
+        <v>52.59133960916441</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08591938018798828</v>
+        <v>10.44300508499146</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2779434303402907</v>
+        <v>0.1637308957578318</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2616875221828251</v>
+        <v>0.1688718910031372</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7561766858252632</v>
+        <v>91.1985454794509</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5882492388088877</v>
+        <v>52.59133960916441</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07013201713562012</v>
+        <v>8.003521919250488</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2766903121172088</v>
+        <v>0.1631195370408529</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2616875221828251</v>
+        <v>0.1688718910031372</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7561766858252632</v>
+        <v>91.1985454794509</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5882492388088877</v>
+        <v>52.59133960916441</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08591938018798828</v>
+        <v>10.44300508499146</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2779434303402907</v>
+        <v>0.1637308957578318</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2616875221828251</v>
+        <v>0.1688718910031372</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7561766858252632</v>
+        <v>91.1985454794509</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5882492388088877</v>
+        <v>52.59133960916441</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.003521919250488</v>
+        <v>0.0965423583984375</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1631195370408529</v>
+        <v>0.909533215133945</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1688718910031372</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G2" t="n">
-        <v>91.1985454794509</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H2" t="n">
-        <v>52.59133960916441</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>10.44300508499146</v>
+        <v>0.1260969638824463</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1637308957578318</v>
+        <v>0.9087632939524625</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1688718910031372</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G3" t="n">
-        <v>91.1985454794509</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H3" t="n">
-        <v>52.59133960916441</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2260673046112061</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9090849528753845</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9131240810741543</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.808430808292843</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.197240504719623</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.003521919250488</v>
+        <v>0.0965423583984375</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1631195370408529</v>
+        <v>0.909533215133945</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1688718910031372</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G2" t="n">
-        <v>91.1985454794509</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H2" t="n">
-        <v>52.59133960916441</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>10.44300508499146</v>
+        <v>0.1260969638824463</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1637308957578318</v>
+        <v>0.9087632939524625</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1688718910031372</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G3" t="n">
-        <v>91.1985454794509</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H3" t="n">
-        <v>52.59133960916441</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2260673046112061</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9090849528753845</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9131240810741543</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.808430808292843</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.197240504719623</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0965423583984375</v>
+        <v>7.145894289016724</v>
       </c>
       <c r="E2" t="n">
-        <v>0.909533215133945</v>
+        <v>0.387611695296131</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133122243111836</v>
+        <v>0.3880771257287021</v>
       </c>
       <c r="G2" t="n">
-        <v>5.802137871795419</v>
+        <v>139.2005370678847</v>
       </c>
       <c r="H2" t="n">
-        <v>4.193872563312008</v>
+        <v>104.7953480310862</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1260969638824463</v>
+        <v>9.151961088180542</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087632939524625</v>
+        <v>0.3875075500335963</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133122243111836</v>
+        <v>0.3880771257287021</v>
       </c>
       <c r="G3" t="n">
-        <v>5.802137871795419</v>
+        <v>139.2005370678847</v>
       </c>
       <c r="H3" t="n">
-        <v>4.193872563312008</v>
+        <v>104.7953480310862</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ElasticNet</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2260673046112061</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9090849528753845</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9131240810741543</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.808430808292843</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.197240504719623</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0965423583984375</v>
+        <v>7.145894289016724</v>
       </c>
       <c r="E2" t="n">
-        <v>0.909533215133945</v>
+        <v>0.387611695296131</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133122243111836</v>
+        <v>0.3880771257287021</v>
       </c>
       <c r="G2" t="n">
-        <v>5.802137871795419</v>
+        <v>139.2005370678847</v>
       </c>
       <c r="H2" t="n">
-        <v>4.193872563312008</v>
+        <v>104.7953480310862</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1260969638824463</v>
+        <v>9.151961088180542</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087632939524625</v>
+        <v>0.3875075500335963</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133122243111836</v>
+        <v>0.3880771257287021</v>
       </c>
       <c r="G3" t="n">
-        <v>5.802137871795419</v>
+        <v>139.2005370678847</v>
       </c>
       <c r="H3" t="n">
-        <v>4.193872563312008</v>
+        <v>104.7953480310862</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ElasticNet</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2260673046112061</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9090849528753845</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9131240810741543</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.808430808292843</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.197240504719623</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.145894289016724</v>
+        <v>0.3807992935180664</v>
       </c>
       <c r="E2" t="n">
-        <v>0.387611695296131</v>
+        <v>0.9900979108184975</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3880771257287021</v>
+        <v>0.9902535164372656</v>
       </c>
       <c r="G2" t="n">
-        <v>139.2005370678847</v>
+        <v>0.9477493659364102</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7953480310862</v>
+        <v>0.7417520659136477</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9.151961088180542</v>
+        <v>0.5139460563659668</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3875075500335963</v>
+        <v>0.9900982946063565</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3880771257287021</v>
+        <v>0.9902535127382041</v>
       </c>
       <c r="G3" t="n">
-        <v>139.2005370678847</v>
+        <v>0.9477495457850106</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7953480310862</v>
+        <v>0.7417454198951648</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.145894289016724</v>
+        <v>0.3807992935180664</v>
       </c>
       <c r="E2" t="n">
-        <v>0.387611695296131</v>
+        <v>0.9900979108184975</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3880771257287021</v>
+        <v>0.9902535164372656</v>
       </c>
       <c r="G2" t="n">
-        <v>139.2005370678847</v>
+        <v>0.9477493659364102</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7953480310862</v>
+        <v>0.7417520659136477</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9.151961088180542</v>
+        <v>0.5139460563659668</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3875075500335963</v>
+        <v>0.9900982946063565</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3880771257287021</v>
+        <v>0.9902535127382041</v>
       </c>
       <c r="G3" t="n">
-        <v>139.2005370678847</v>
+        <v>0.9477495457850106</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7953480310862</v>
+        <v>0.7417454198951648</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3807992935180664</v>
+        <v>7.956679582595825</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9900979108184975</v>
+        <v>0.1631195370408529</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9902535164372656</v>
+        <v>0.1688718910031372</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9477493659364102</v>
+        <v>91.1985454794509</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7417520659136477</v>
+        <v>52.59133960916441</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5139460563659668</v>
+        <v>10.55267238616943</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9900982946063565</v>
+        <v>0.1637308957578318</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9902535127382041</v>
+        <v>0.1688718910031372</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9477495457850106</v>
+        <v>91.1985454794509</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7417454198951648</v>
+        <v>52.59133960916441</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3807992935180664</v>
+        <v>7.956679582595825</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9900979108184975</v>
+        <v>0.1631195370408529</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9902535164372656</v>
+        <v>0.1688718910031372</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9477493659364102</v>
+        <v>91.1985454794509</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7417520659136477</v>
+        <v>52.59133960916441</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5139460563659668</v>
+        <v>10.55267238616943</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9900982946063565</v>
+        <v>0.1637308957578318</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9902535127382041</v>
+        <v>0.1688718910031372</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9477495457850106</v>
+        <v>91.1985454794509</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7417454198951648</v>
+        <v>52.59133960916441</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.956679582595825</v>
+        <v>199.4946460723877</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1631195370408529</v>
+        <v>0.7327682996256856</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1688718910031372</v>
+        <v>0.7359707138489484</v>
       </c>
       <c r="G2" t="n">
-        <v>91.1985454794509</v>
+        <v>17.43327136693664</v>
       </c>
       <c r="H2" t="n">
-        <v>52.59133960916441</v>
+        <v>13.23667225137099</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>10.55267238616943</v>
+        <v>247.0868356227875</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1637308957578318</v>
+        <v>0.7328899937014212</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1688718910031372</v>
+        <v>0.7359707138489484</v>
       </c>
       <c r="G3" t="n">
-        <v>91.1985454794509</v>
+        <v>17.43327136693664</v>
       </c>
       <c r="H3" t="n">
-        <v>52.59133960916441</v>
+        <v>13.23667225137099</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.956679582595825</v>
+        <v>199.4946460723877</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1631195370408529</v>
+        <v>0.7327682996256856</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1688718910031372</v>
+        <v>0.7359707138489484</v>
       </c>
       <c r="G2" t="n">
-        <v>91.1985454794509</v>
+        <v>17.43327136693664</v>
       </c>
       <c r="H2" t="n">
-        <v>52.59133960916441</v>
+        <v>13.23667225137099</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>10.55267238616943</v>
+        <v>247.0868356227875</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1637308957578318</v>
+        <v>0.7328899937014212</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1688718910031372</v>
+        <v>0.7359707138489484</v>
       </c>
       <c r="G3" t="n">
-        <v>91.1985454794509</v>
+        <v>17.43327136693664</v>
       </c>
       <c r="H3" t="n">
-        <v>52.59133960916441</v>
+        <v>13.23667225137099</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>199.4946460723877</v>
+        <v>0.08172798156738281</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7327682996256856</v>
+        <v>0.2766903121172088</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7359707138489484</v>
+        <v>0.2616875221828251</v>
       </c>
       <c r="G2" t="n">
-        <v>17.43327136693664</v>
+        <v>0.7561766858252632</v>
       </c>
       <c r="H2" t="n">
-        <v>13.23667225137099</v>
+        <v>0.5882492388088877</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'alpha': 0.01, 'l1_ratio': 0.1, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>247.0868356227875</v>
+        <v>0.1224496364593506</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7328899937014212</v>
+        <v>0.2779434303402907</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7359707138489484</v>
+        <v>0.2616875221828251</v>
       </c>
       <c r="G3" t="n">
-        <v>17.43327136693664</v>
+        <v>0.7561766858252632</v>
       </c>
       <c r="H3" t="n">
-        <v>13.23667225137099</v>
+        <v>0.5882492388088877</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'alpha': 0.01, 'l1_ratio': 0.1, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>199.4946460723877</v>
+        <v>0.08172798156738281</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7327682996256856</v>
+        <v>0.2766903121172088</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7359707138489484</v>
+        <v>0.2616875221828251</v>
       </c>
       <c r="G2" t="n">
-        <v>17.43327136693664</v>
+        <v>0.7561766858252632</v>
       </c>
       <c r="H2" t="n">
-        <v>13.23667225137099</v>
+        <v>0.5882492388088877</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'alpha': 0.01, 'l1_ratio': 0.1, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>247.0868356227875</v>
+        <v>0.1224496364593506</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7328899937014212</v>
+        <v>0.2779434303402907</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7359707138489484</v>
+        <v>0.2616875221828251</v>
       </c>
       <c r="G3" t="n">
-        <v>17.43327136693664</v>
+        <v>0.7561766858252632</v>
       </c>
       <c r="H3" t="n">
-        <v>13.23667225137099</v>
+        <v>0.5882492388088877</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'alpha': 0.01, 'l1_ratio': 0.1, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08172798156738281</v>
+        <v>0.08484387397766113</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2766903121172088</v>
+        <v>0.909533215133945</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2616875221828251</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7561766858252632</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5882492388088877</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.01, 'l1_ratio': 0.1, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1224496364593506</v>
+        <v>0.1227543354034424</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2779434303402907</v>
+        <v>0.9087632939524625</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2616875221828251</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7561766858252632</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5882492388088877</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.01, 'l1_ratio': 0.1, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1999638080596924</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9090849528753845</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9131240810741543</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.808430808292843</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.197240504719623</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08172798156738281</v>
+        <v>0.08484387397766113</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2766903121172088</v>
+        <v>0.909533215133945</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2616875221828251</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7561766858252632</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5882492388088877</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.01, 'l1_ratio': 0.1, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1224496364593506</v>
+        <v>0.1227543354034424</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2779434303402907</v>
+        <v>0.9087632939524625</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2616875221828251</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7561766858252632</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5882492388088877</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.01, 'l1_ratio': 0.1, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1999638080596924</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9090849528753845</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9131240810741543</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.808430808292843</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.197240504719623</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08484387397766113</v>
+        <v>0.1466038227081299</v>
       </c>
       <c r="E2" t="n">
         <v>0.909533215133945</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1227543354034424</v>
+        <v>0.1362264156341553</v>
       </c>
       <c r="E3" t="n">
         <v>0.9087632939524625</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1999638080596924</v>
+        <v>0.2890579700469971</v>
       </c>
       <c r="E4" t="n">
         <v>0.9090849528753845</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08484387397766113</v>
+        <v>0.1466038227081299</v>
       </c>
       <c r="E2" t="n">
         <v>0.909533215133945</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1227543354034424</v>
+        <v>0.1362264156341553</v>
       </c>
       <c r="E3" t="n">
         <v>0.9087632939524625</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1999638080596924</v>
+        <v>0.2890579700469971</v>
       </c>
       <c r="E4" t="n">
         <v>0.9090849528753845</v>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1466038227081299</v>
+        <v>0.8618404865264893</v>
       </c>
       <c r="E2" t="n">
-        <v>0.909533215133945</v>
+        <v>0.3880221697468028</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133122243111836</v>
+        <v>0.378311815589937</v>
       </c>
       <c r="G2" t="n">
-        <v>5.802137871795419</v>
+        <v>105.158649292119</v>
       </c>
       <c r="H2" t="n">
-        <v>4.193872563312008</v>
+        <v>79.46228555504133</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.9, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1362264156341553</v>
+        <v>1.384314060211182</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087632939524625</v>
+        <v>0.3876606679499853</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133122243111836</v>
+        <v>0.378311815589937</v>
       </c>
       <c r="G3" t="n">
-        <v>5.802137871795419</v>
+        <v>105.158649292119</v>
       </c>
       <c r="H3" t="n">
-        <v>4.193872563312008</v>
+        <v>79.46228555504133</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ElasticNet</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2890579700469971</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9090849528753845</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9131240810741543</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.808430808292843</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.197240504719623</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.9, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1466038227081299</v>
+        <v>0.8618404865264893</v>
       </c>
       <c r="E2" t="n">
-        <v>0.909533215133945</v>
+        <v>0.3880221697468028</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133122243111836</v>
+        <v>0.378311815589937</v>
       </c>
       <c r="G2" t="n">
-        <v>5.802137871795419</v>
+        <v>105.158649292119</v>
       </c>
       <c r="H2" t="n">
-        <v>4.193872563312008</v>
+        <v>79.46228555504133</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.9, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1362264156341553</v>
+        <v>1.384314060211182</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087632939524625</v>
+        <v>0.3876606679499853</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133122243111836</v>
+        <v>0.378311815589937</v>
       </c>
       <c r="G3" t="n">
-        <v>5.802137871795419</v>
+        <v>105.158649292119</v>
       </c>
       <c r="H3" t="n">
-        <v>4.193872563312008</v>
+        <v>79.46228555504133</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ElasticNet</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2890579700469971</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9090849528753845</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9131240810741543</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.808430808292843</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.197240504719623</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.9, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8618404865264893</v>
+        <v>0.1181185245513916</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3880221697468028</v>
+        <v>0.909533215133945</v>
       </c>
       <c r="F2" t="n">
-        <v>0.378311815589937</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G2" t="n">
-        <v>105.158649292119</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H2" t="n">
-        <v>79.46228555504133</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.9, 'alpha': 0.1}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.384314060211182</v>
+        <v>0.09784483909606934</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3876606679499853</v>
+        <v>0.9087632939524625</v>
       </c>
       <c r="F3" t="n">
-        <v>0.378311815589937</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G3" t="n">
-        <v>105.158649292119</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H3" t="n">
-        <v>79.46228555504133</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.9, 'alpha': 0.1}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2399892807006836</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9090849528753845</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9131240810741543</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.808430808292843</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.197240504719623</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,26 +654,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8618404865264893</v>
+        <v>0.1181185245513916</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3880221697468028</v>
+        <v>0.909533215133945</v>
       </c>
       <c r="F2" t="n">
-        <v>0.378311815589937</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G2" t="n">
-        <v>105.158649292119</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H2" t="n">
-        <v>79.46228555504133</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.9, 'alpha': 0.1}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -654,26 +689,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.384314060211182</v>
+        <v>0.09784483909606934</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3876606679499853</v>
+        <v>0.9087632939524625</v>
       </c>
       <c r="F3" t="n">
-        <v>0.378311815589937</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G3" t="n">
-        <v>105.158649292119</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H3" t="n">
-        <v>79.46228555504133</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.9, 'alpha': 0.1}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2399892807006836</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9090849528753845</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9131240810741543</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.808430808292843</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.197240504719623</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1181185245513916</v>
+        <v>0.3873200416564941</v>
       </c>
       <c r="E2" t="n">
-        <v>0.909533215133945</v>
+        <v>0.9913128938769532</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133122243111836</v>
+        <v>0.9911884119642234</v>
       </c>
       <c r="G2" t="n">
-        <v>5.802137871795419</v>
+        <v>0.8901671098299406</v>
       </c>
       <c r="H2" t="n">
-        <v>4.193872563312008</v>
+        <v>0.7027435502511595</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09784483909606934</v>
+        <v>0.4760627746582031</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087632939524625</v>
+        <v>0.9913120707267371</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133122243111836</v>
+        <v>0.9911884119642234</v>
       </c>
       <c r="G3" t="n">
-        <v>5.802137871795419</v>
+        <v>0.8901671098299406</v>
       </c>
       <c r="H3" t="n">
-        <v>4.193872563312008</v>
+        <v>0.7027435502511595</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ElasticNet</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2399892807006836</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9090849528753845</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9131240810741543</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.808430808292843</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.197240504719623</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1181185245513916</v>
+        <v>0.3873200416564941</v>
       </c>
       <c r="E2" t="n">
-        <v>0.909533215133945</v>
+        <v>0.9913128938769532</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133122243111836</v>
+        <v>0.9911884119642234</v>
       </c>
       <c r="G2" t="n">
-        <v>5.802137871795419</v>
+        <v>0.8901671098299406</v>
       </c>
       <c r="H2" t="n">
-        <v>4.193872563312008</v>
+        <v>0.7027435502511595</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09784483909606934</v>
+        <v>0.4760627746582031</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087632939524625</v>
+        <v>0.9913120707267371</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133122243111836</v>
+        <v>0.9911884119642234</v>
       </c>
       <c r="G3" t="n">
-        <v>5.802137871795419</v>
+        <v>0.8901671098299406</v>
       </c>
       <c r="H3" t="n">
-        <v>4.193872563312008</v>
+        <v>0.7027435502511595</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ElasticNet</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2399892807006836</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9090849528753845</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9131240810741543</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.808430808292843</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.197240504719623</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_ElasticNet_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3873200416564941</v>
+        <v>0.371823787689209</v>
       </c>
       <c r="E2" t="n">
         <v>0.9913128938769532</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4760627746582031</v>
+        <v>0.4821679592132568</v>
       </c>
       <c r="E3" t="n">
         <v>0.9913120707267371</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3873200416564941</v>
+        <v>0.371823787689209</v>
       </c>
       <c r="E2" t="n">
         <v>0.9913128938769532</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4760627746582031</v>
+        <v>0.4821679592132568</v>
       </c>
       <c r="E3" t="n">
         <v>0.9913120707267371</v>
